--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12ACBD4C-2ED1-4122-AE44-01E67618E573}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79F5F96-E550-4D1F-A9A4-1D17504A8004}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -117,10 +117,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="7"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -470,13 +470,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -487,7 +487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -507,13 +507,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -524,18 +524,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -546,7 +546,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -557,7 +557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -568,7 +568,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -588,13 +588,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -602,7 +602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -610,7 +610,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -618,27 +618,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>10</v>
       </c>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79F5F96-E550-4D1F-A9A4-1D17504A8004}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3253C1BE-13E5-46CB-A014-B00CE0E4AE12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Edition" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Edition1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -652,4 +653,73 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3253C1BE-13E5-46CB-A014-B00CE0E4AE12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5CE9BE-8928-4F64-9C14-E16D5ECE8FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
     <sheet name="Edition" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
     <sheet name="Edition1" sheetId="5" r:id="rId4"/>
+    <sheet name="Form_Edit" sheetId="6" r:id="rId5"/>
+    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="38">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -103,13 +105,52 @@
   </si>
   <si>
     <t>Agreement5__c</t>
+  </si>
+  <si>
+    <t>fieldQuestion1__c</t>
+  </si>
+  <si>
+    <t>Automation Test</t>
+  </si>
+  <si>
+    <t>fieldQuestion3__c</t>
+  </si>
+  <si>
+    <t>fieldsbirEmpNumber__c</t>
+  </si>
+  <si>
+    <t>fieldExperienceLevel__c</t>
+  </si>
+  <si>
+    <t>0-5 years</t>
+  </si>
+  <si>
+    <t>fieldAppplicationSubmitted__c</t>
+  </si>
+  <si>
+    <t>fieldSubmittedOnForm__c</t>
+  </si>
+  <si>
+    <t>fieldRevisionDueDate__c</t>
+  </si>
+  <si>
+    <t>fieldPreApplicationSectionsforRevision__c</t>
+  </si>
+  <si>
+    <t>fieldExplanationOfRevisionsNeeded__c</t>
+  </si>
+  <si>
+    <t>Negotiation Initiated</t>
+  </si>
+  <si>
+    <t>Files and Forms: Forms</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,6 +161,12 @@
     <font>
       <sz val="7"/>
       <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -144,7 +191,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -156,6 +203,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -471,13 +519,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -508,13 +556,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -525,7 +573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -536,7 +584,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -547,7 +595,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -558,7 +606,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -569,7 +617,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -589,13 +637,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -603,7 +651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -611,7 +659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -619,27 +667,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -658,13 +706,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -686,7 +734,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -697,7 +745,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -708,7 +756,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -717,6 +765,155 @@
       </c>
       <c r="C5" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="43.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE5CE9BE-8928-4F64-9C14-E16D5ECE8FF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C276F49-2BBD-48F1-86B9-3B8CE3974B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,10 @@
     <sheet name="Edition1" sheetId="5" r:id="rId4"/>
     <sheet name="Form_Edit" sheetId="6" r:id="rId5"/>
     <sheet name="Negotiation_Edit" sheetId="7" r:id="rId6"/>
+    <sheet name="Nego_Edit1" sheetId="8" r:id="rId7"/>
+    <sheet name="FileFormForms" sheetId="9" r:id="rId8"/>
+    <sheet name="FileFormForms1" sheetId="10" r:id="rId9"/>
+    <sheet name="FileFormForms2" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -30,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="44">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -144,13 +148,31 @@
   </si>
   <si>
     <t>Files and Forms: Forms</t>
+  </si>
+  <si>
+    <t>Overview Tab: Pre-Application Overview</t>
+  </si>
+  <si>
+    <t>Overview Tab: Project Information</t>
+  </si>
+  <si>
+    <t>Files and Forms: Pre Application Files</t>
+  </si>
+  <si>
+    <t>Budget Tab: Focus Area</t>
+  </si>
+  <si>
+    <t>Budget Tab: Budget Details</t>
+  </si>
+  <si>
+    <t>Budget Tab: Narrative</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -168,6 +190,13 @@
       <sz val="9"/>
       <color rgb="FF202124"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -191,7 +220,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -204,6 +233,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,13 +551,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -536,7 +568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -553,16 +585,129 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,7 +718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -584,7 +729,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -595,7 +740,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -606,7 +751,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -617,7 +762,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -637,13 +782,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -651,7 +796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -659,7 +804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -667,27 +812,27 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="B7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -706,13 +851,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="21.85546875" customWidth="1"/>
     <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -723,7 +868,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -734,7 +879,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -745,7 +890,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -756,7 +901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
@@ -775,13 +920,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.5703125" customWidth="1"/>
     <col min="3" max="3" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -792,7 +937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -803,7 +948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -814,7 +959,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -825,7 +970,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -836,7 +981,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -847,7 +992,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -866,13 +1011,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="43.7109375" customWidth="1"/>
     <col min="3" max="3" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -883,7 +1028,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -894,7 +1039,7 @@
         <v>43707</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -905,7 +1050,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -914,6 +1059,182 @@
       </c>
       <c r="C4" t="s">
         <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3">
+        <v>43707</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workplace\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C276F49-2BBD-48F1-86B9-3B8CE3974B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FE1036-B13C-4CC9-A411-F4D0E3CB33E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="9" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,8 @@
     <sheet name="FileFormForms" sheetId="9" r:id="rId8"/>
     <sheet name="FileFormForms1" sheetId="10" r:id="rId9"/>
     <sheet name="FileFormForms2" sheetId="11" r:id="rId10"/>
+    <sheet name="Edition_v" sheetId="12" r:id="rId11"/>
+    <sheet name="Form_v" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="49">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -166,13 +168,28 @@
   </si>
   <si>
     <t>Budget Tab: Narrative</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>Automation Announcement</t>
+  </si>
+  <si>
+    <t>Negotiations</t>
+  </si>
+  <si>
+    <t>fieldApplicantResponse__c</t>
+  </si>
+  <si>
+    <t>Automation Testing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -199,6 +216,12 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF202124"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -220,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -236,6 +259,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -551,10 +575,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -588,10 +612,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -698,13 +722,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -714,6 +738,166 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
@@ -782,10 +966,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -851,10 +1035,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -920,10 +1104,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1011,10 +1195,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.7109375" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="43.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1070,10 +1254,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1151,10 +1335,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1198,10 +1382,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workplace\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FE1036-B13C-4CC9-A411-F4D0E3CB33E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE19ACD7-0C7E-4C45-A345-05EAB331F4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,7 @@
     <sheet name="FileFormForms2" sheetId="11" r:id="rId10"/>
     <sheet name="Edition_v" sheetId="12" r:id="rId11"/>
     <sheet name="Form_v" sheetId="13" r:id="rId12"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -882,6 +883,15 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3138A0C3-1513-47D0-A3EC-31C39339B2A3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24701"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workplace\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE19ACD7-0C7E-4C45-A345-05EAB331F4AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AF3C0B-335B-4A82-8F69-352812868F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="5" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,6 @@
     <sheet name="FileFormForms2" sheetId="11" r:id="rId10"/>
     <sheet name="Edition_v" sheetId="12" r:id="rId11"/>
     <sheet name="Form_v" sheetId="13" r:id="rId12"/>
-    <sheet name="Sheet2" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -883,15 +882,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3138A0C3-1513-47D0-A3EC-31C39339B2A3}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workplace\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AF3C0B-335B-4A82-8F69-352812868F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58D2EF8-A829-4487-A104-3C77BBF9599B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="53">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -110,9 +110,6 @@
     <t>Checked</t>
   </si>
   <si>
-    <t>Agreement5__c</t>
-  </si>
-  <si>
     <t>fieldQuestion1__c</t>
   </si>
   <si>
@@ -183,25 +180,34 @@
   </si>
   <si>
     <t>Automation Testing</t>
+  </si>
+  <si>
+    <t>fieldAgreement5__c</t>
+  </si>
+  <si>
+    <t>fieldJustification__c</t>
+  </si>
+  <si>
+    <t>fieldProjectBeneficiaries__c</t>
+  </si>
+  <si>
+    <t>fieldProjectGoal__c</t>
+  </si>
+  <si>
+    <t>fieldProjectAbstract__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF222222"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="9"/>
@@ -243,7 +249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -255,11 +261,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -633,8 +638,8 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -644,77 +649,77 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>39</v>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>41</v>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>42</v>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>43</v>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>40</v>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
         <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -746,11 +751,11 @@
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -788,13 +793,13 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C6" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -826,52 +831,52 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>27</v>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>31</v>
+      <c r="B5" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>32</v>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -906,8 +911,8 @@
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>15</v>
+      <c r="B2" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
@@ -917,8 +922,8 @@
       <c r="A3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>16</v>
+      <c r="B3" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
@@ -928,8 +933,8 @@
       <c r="A4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>17</v>
+      <c r="B4" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -939,8 +944,8 @@
       <c r="A5" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>24</v>
+      <c r="B5" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -950,8 +955,8 @@
       <c r="A6" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>14</v>
+      <c r="B6" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -1125,30 +1130,30 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>27</v>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>28</v>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -1158,30 +1163,30 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>31</v>
+      <c r="B6" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
+      <c r="B7" s="4" t="s">
+        <v>31</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1216,8 +1221,8 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -1227,22 +1232,22 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1275,8 +1280,8 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -1286,44 +1291,44 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>39</v>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>40</v>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
         <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1356,22 +1361,22 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>34</v>
+      <c r="B2" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
         <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1403,19 +1408,19 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>34</v>
+      <c r="B2" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>33</v>
+      <c r="B3" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C3">
         <v>43707</v>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C58D2EF8-A829-4487-A104-3C77BBF9599B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B050411-9237-4C1C-93B7-DDEEB9634845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Edition" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
-    <sheet name="Edition1" sheetId="5" r:id="rId4"/>
-    <sheet name="Form_Edit" sheetId="6" r:id="rId5"/>
-    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId6"/>
-    <sheet name="Nego_Edit1" sheetId="8" r:id="rId7"/>
-    <sheet name="FileFormForms" sheetId="9" r:id="rId8"/>
-    <sheet name="FileFormForms1" sheetId="10" r:id="rId9"/>
-    <sheet name="FileFormForms2" sheetId="11" r:id="rId10"/>
-    <sheet name="Edition_v" sheetId="12" r:id="rId11"/>
-    <sheet name="Form_v" sheetId="13" r:id="rId12"/>
+    <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
+    <sheet name="Creation" sheetId="1" r:id="rId2"/>
+    <sheet name="Edition" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
+    <sheet name="Edition1" sheetId="5" r:id="rId5"/>
+    <sheet name="Form_Edit" sheetId="6" r:id="rId6"/>
+    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId7"/>
+    <sheet name="Nego_Edit1" sheetId="8" r:id="rId8"/>
+    <sheet name="FileFormForms" sheetId="9" r:id="rId9"/>
+    <sheet name="FileFormForms1" sheetId="10" r:id="rId10"/>
+    <sheet name="FileFormForms2" sheetId="11" r:id="rId11"/>
+    <sheet name="Edition_v" sheetId="12" r:id="rId12"/>
+    <sheet name="Form_v" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="54">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -195,13 +196,16 @@
   </si>
   <si>
     <t>fieldProjectAbstract__c</t>
+  </si>
+  <si>
+    <t>Budget Tab: Budget Summary by Focus Area</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,6 +232,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -249,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -265,6 +275,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -578,6 +591,395 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61A50-F37E-45CB-A9C9-9EE192BF6C64}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>43707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -614,280 +1016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -968,7 +1097,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1037,7 +1166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1106,7 +1235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1197,7 +1326,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1256,7 +1385,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1337,7 +1466,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1382,51 +1511,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3">
-        <v>43707</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B050411-9237-4C1C-93B7-DDEEB9634845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05852B30-0234-4815-B040-0AE862960700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05852B30-0234-4815-B040-0AE862960700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370572EF-C762-43F3-A744-DFB3E18C2E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{370572EF-C762-43F3-A744-DFB3E18C2E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEC1F61-9896-41A5-91BB-14685F58B924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEC1F61-9896-41A5-91BB-14685F58B924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527F681E-7130-402B-9BC0-8B29CA54D084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -20,12 +20,13 @@
     <sheet name="Edition1" sheetId="5" r:id="rId5"/>
     <sheet name="Form_Edit" sheetId="6" r:id="rId6"/>
     <sheet name="Negotiation_Edit" sheetId="7" r:id="rId7"/>
-    <sheet name="Nego_Edit1" sheetId="8" r:id="rId8"/>
-    <sheet name="FileFormForms" sheetId="9" r:id="rId9"/>
-    <sheet name="FileFormForms1" sheetId="10" r:id="rId10"/>
-    <sheet name="FileFormForms2" sheetId="11" r:id="rId11"/>
-    <sheet name="Edition_v" sheetId="12" r:id="rId12"/>
-    <sheet name="Form_v" sheetId="13" r:id="rId13"/>
+    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId8"/>
+    <sheet name="Nego_Edit1" sheetId="8" r:id="rId9"/>
+    <sheet name="FileFormForms" sheetId="9" r:id="rId10"/>
+    <sheet name="FileFormForms1" sheetId="10" r:id="rId11"/>
+    <sheet name="FileFormForms2" sheetId="11" r:id="rId12"/>
+    <sheet name="Edition_v" sheetId="12" r:id="rId13"/>
+    <sheet name="Form_v" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="55">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -199,6 +200,9 @@
   </si>
   <si>
     <t>Budget Tab: Budget Summary by Focus Area</t>
+  </si>
+  <si>
+    <t>Files and Forms: Notes</t>
   </si>
 </sst>
 </file>
@@ -593,10 +597,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61A50-F37E-45CB-A9C9-9EE192BF6C64}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -660,12 +664,12 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -695,10 +699,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3">
-        <v>43707</v>
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -707,12 +711,12 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -731,10 +735,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -742,76 +746,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>43707</v>
       </c>
     </row>
   </sheetData>
@@ -820,12 +758,12 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -840,58 +778,91 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>44</v>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>47</v>
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -900,12 +871,12 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -920,58 +891,58 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>29</v>
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -979,13 +950,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -995,7 +966,7 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1003,26 +974,69 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1032,63 +1046,19 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>52</v>
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1097,13 +1067,94 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1169,10 +1220,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1238,10 +1289,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1329,10 +1380,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="43.6328125" customWidth="1"/>
+    <col min="3" max="3" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1386,12 +1437,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652FB01D-588D-4E1E-B4E4-BDE81F8D2A81}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1423,8 +1474,8 @@
       <c r="B3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>37</v>
+      <c r="C3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1434,8 +1485,8 @@
       <c r="B4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>38</v>
+      <c r="C4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1443,36 +1494,24 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C5" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1491,10 +1530,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1502,13 +1541,47 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C6" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\version Test\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductClassic\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{527F681E-7130-402B-9BC0-8B29CA54D084}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F932A1-CB9F-40EF-910E-5C8DCE140DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -18,15 +18,16 @@
     <sheet name="Edition" sheetId="4" r:id="rId3"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
     <sheet name="Edition1" sheetId="5" r:id="rId5"/>
-    <sheet name="Form_Edit" sheetId="6" r:id="rId6"/>
-    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId7"/>
-    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId8"/>
-    <sheet name="Nego_Edit1" sheetId="8" r:id="rId9"/>
-    <sheet name="FileFormForms" sheetId="9" r:id="rId10"/>
-    <sheet name="FileFormForms1" sheetId="10" r:id="rId11"/>
-    <sheet name="FileFormForms2" sheetId="11" r:id="rId12"/>
-    <sheet name="Edition_v" sheetId="12" r:id="rId13"/>
-    <sheet name="Form_v" sheetId="13" r:id="rId14"/>
+    <sheet name="Form_EditNewValidate" sheetId="17" r:id="rId6"/>
+    <sheet name="Form_Edit" sheetId="6" r:id="rId7"/>
+    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId8"/>
+    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId9"/>
+    <sheet name="Nego_Edit1" sheetId="8" r:id="rId10"/>
+    <sheet name="FileFormForms" sheetId="9" r:id="rId11"/>
+    <sheet name="FileFormForms1" sheetId="10" r:id="rId12"/>
+    <sheet name="FileFormForms2" sheetId="11" r:id="rId13"/>
+    <sheet name="Edition_v" sheetId="12" r:id="rId14"/>
+    <sheet name="Form_v" sheetId="13" r:id="rId15"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="55">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -300,9 +301,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -340,7 +341,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -446,7 +447,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -588,7 +589,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -597,10 +598,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61A50-F37E-45CB-A9C9-9EE192BF6C64}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -664,12 +665,12 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -688,10 +689,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -699,24 +700,58 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C6" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -746,10 +781,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3">
-        <v>43707</v>
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -758,12 +793,12 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -782,10 +817,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -793,76 +828,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>43707</v>
       </c>
     </row>
   </sheetData>
@@ -871,12 +840,12 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -891,58 +860,91 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>44</v>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>47</v>
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -951,12 +953,12 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -971,58 +973,58 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>29</v>
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>25</v>
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1030,13 +1032,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1046,7 +1048,7 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1054,26 +1056,69 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1083,63 +1128,19 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>52</v>
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1148,13 +1149,94 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1220,10 +1302,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1287,12 +1369,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD30DDC9-54F2-4EA2-B2D6-C4D0607FC1E9}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.36328125" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1322,54 +1403,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1378,12 +1415,12 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.6328125" customWidth="1"/>
-    <col min="3" max="3" width="22.54296875" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1402,10 +1439,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1413,10 +1450,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1424,25 +1461,57 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652FB01D-588D-4E1E-B4E4-BDE81F8D2A81}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1483,35 +1552,25 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652FB01D-588D-4E1E-B4E4-BDE81F8D2A81}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1543,8 +1602,8 @@
       <c r="B3" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>37</v>
+      <c r="C3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1554,8 +1613,8 @@
       <c r="B4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>38</v>
+      <c r="C4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1563,25 +1622,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C5" t="s">
         <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>